--- a/02_Zero_Shot/outputs/Embedding/DistilBERT-base-uncased/RESULT_pan_distilbert-base-uncased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/DistilBERT-base-uncased/RESULT_pan_distilbert-base-uncased_zeroshot.xlsx
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.445847496000169</v>
+        <v>9.341557214000204</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001040178054676381</v>
+        <v>0.006720544758273528</v>
       </c>
     </row>
   </sheetData>
